--- a/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0003T0006Z000C1N36_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0003T0006Z000C1N36_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>31.66111455298476</v>
+        <v>5.144931114860023</v>
       </c>
       <c r="D2" t="n">
-        <v>37.57864563954717</v>
+        <v>6.106529916426415</v>
       </c>
       <c r="E2" t="n">
-        <v>1.36214272858852</v>
+        <v>0.2213481933956345</v>
       </c>
       <c r="F2" t="n">
-        <v>7.098733001435125</v>
+        <v>1.153544112733208</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>28.93682909580772</v>
+        <v>4.702234728068754</v>
       </c>
       <c r="D3" t="n">
-        <v>23.38117963667692</v>
+        <v>3.799441690959999</v>
       </c>
       <c r="E3" t="n">
-        <v>1.36214272858852</v>
+        <v>0.2213481933956345</v>
       </c>
       <c r="F3" t="n">
-        <v>7.098733001435125</v>
+        <v>1.153544112733208</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
